--- a/26-07-23_optowell_test2/t5.xlsx
+++ b/26-07-23_optowell_test2/t5.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dungeon\Desktop\Yuhang\26-07-18 optowell exp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dungeon\Desktop\Yuhang\26-07-22 optowell exp 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0570E237-435B-4CB6-A45C-B4E27CB2B9D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD409242-02E1-4078-8595-B8C9D4C7914C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{50F3D6EA-8382-4725-AF1E-1478541DF273}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{DAC16DAD-F86E-4C58-AEE9-820392803FAC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -45,7 +45,7 @@
     <author>dungeon</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{8E81ADA4-4701-4AA2-8562-1DB28C8C8284}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{BBC665D3-159A-4DF2-9228-2F92AD2270E2}">
       <text>
         <r>
           <rPr>
@@ -110,7 +110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{D661B521-67B5-403E-B8E2-D177792F82F6}">
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{3E0421F5-0C6B-4233-87E6-230FF9CB145E}">
       <text>
         <r>
           <rPr>
@@ -136,7 +136,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="58">
   <si>
     <t>Application: Tecan i-control</t>
   </si>
@@ -162,13 +162,13 @@
     <t>Date:</t>
   </si>
   <si>
-    <t>18/07/2026</t>
+    <t>22/07/2026</t>
   </si>
   <si>
     <t>Time:</t>
   </si>
   <si>
-    <t>19:40:44</t>
+    <t>16:59:36</t>
   </si>
   <si>
     <t>System</t>
@@ -222,10 +222,10 @@
     <t>Start Time:</t>
   </si>
   <si>
-    <t>18/07/2026 19:40:44</t>
-  </si>
-  <si>
-    <t>Temperature: 37.4 °C</t>
+    <t>22/07/2026 16:59:36</t>
+  </si>
+  <si>
+    <t>Temperature: 28.3 °C</t>
   </si>
   <si>
     <t>&lt;&gt;</t>
@@ -258,7 +258,7 @@
     <t>End Time:</t>
   </si>
   <si>
-    <t>18/07/2026 19:42:06</t>
+    <t>22/07/2026 17:00:57</t>
   </si>
   <si>
     <t>Label: GFP 395nm</t>
@@ -294,25 +294,22 @@
     <t>Lag Time</t>
   </si>
   <si>
-    <t>18/07/2026 19:42:08</t>
-  </si>
-  <si>
-    <t>Temperature: 37.3 °C</t>
-  </si>
-  <si>
-    <t>18/07/2026 19:43:26</t>
+    <t>22/07/2026 17:01:00</t>
+  </si>
+  <si>
+    <t>Temperature: 28.4 °C</t>
+  </si>
+  <si>
+    <t>22/07/2026 17:02:17</t>
   </si>
   <si>
     <t>Label: GFP 480nm</t>
   </si>
   <si>
-    <t>18/07/2026 19:43:31</t>
-  </si>
-  <si>
-    <t>Temperature: 37.5 °C</t>
-  </si>
-  <si>
-    <t>18/07/2026 19:44:49</t>
+    <t>22/07/2026 17:02:23</t>
+  </si>
+  <si>
+    <t>22/07/2026 17:03:40</t>
   </si>
 </sst>
 </file>
@@ -485,13 +482,13 @@
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Tecan.At.Excel.Attenuation" xfId="6" xr:uid="{0C29F3B3-5CC0-43FE-99A9-65BBB3DAB9A4}"/>
-    <cellStyle name="Tecan.At.Excel.AutoGain_0" xfId="7" xr:uid="{DC4B6468-445C-4B34-B2EA-0DE292EBF5CE}"/>
-    <cellStyle name="Tecan.At.Excel.Error" xfId="1" xr:uid="{E259DCBC-A41D-4DBA-B236-82C9FA7B5D81}"/>
-    <cellStyle name="Tecan.At.Excel.GFactorAndMeasurementBlank" xfId="5" xr:uid="{32223138-B7C1-4A32-83E0-09C7EDB83544}"/>
-    <cellStyle name="Tecan.At.Excel.GFactorBlank" xfId="3" xr:uid="{2CA12A7A-360C-4A32-B432-26DAAABFFCAC}"/>
-    <cellStyle name="Tecan.At.Excel.GFactorReference" xfId="4" xr:uid="{430887D0-9774-41D2-8A78-AC96E51DB909}"/>
-    <cellStyle name="Tecan.At.Excel.MeasurementBlank" xfId="2" xr:uid="{826BCAEA-09F8-49DE-8C9D-9FCE3826F524}"/>
+    <cellStyle name="Tecan.At.Excel.Attenuation" xfId="6" xr:uid="{40C0A20E-B324-498D-ABD7-D991AFD957A5}"/>
+    <cellStyle name="Tecan.At.Excel.AutoGain_0" xfId="7" xr:uid="{5441BBEA-DAA9-4E3E-A117-F48A6835D5BB}"/>
+    <cellStyle name="Tecan.At.Excel.Error" xfId="1" xr:uid="{7EC7139B-ADEF-47DD-A88B-702627BF381F}"/>
+    <cellStyle name="Tecan.At.Excel.GFactorAndMeasurementBlank" xfId="5" xr:uid="{D56926E8-8E64-4D8E-8121-300C0BC68DEE}"/>
+    <cellStyle name="Tecan.At.Excel.GFactorBlank" xfId="3" xr:uid="{6A4C45F9-44F5-4ACA-943E-E8D6ECB06813}"/>
+    <cellStyle name="Tecan.At.Excel.GFactorReference" xfId="4" xr:uid="{F05AA019-C1E0-4E71-99E6-9AC1B15DEDC6}"/>
+    <cellStyle name="Tecan.At.Excel.MeasurementBlank" xfId="2" xr:uid="{EC9B4C7A-066D-492B-9DBF-E3C18C6167A6}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -822,7 +819,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47727E20-24F2-4A49-89C8-BCD1AF8B5C88}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D8E7983-D796-4FE7-9167-76466B1A9E69}">
   <dimension ref="A1:M101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1011,40 +1008,40 @@
         <v>31</v>
       </c>
       <c r="B25">
-        <v>0.14599999785423279</v>
+        <v>0.15240000188350677</v>
       </c>
       <c r="C25">
-        <v>0.14839999377727509</v>
+        <v>0.16449999809265137</v>
       </c>
       <c r="D25">
-        <v>0.14900000393390656</v>
+        <v>0.17229999601840973</v>
       </c>
       <c r="E25">
-        <v>0.12860000133514404</v>
+        <v>0.18279999494552612</v>
       </c>
       <c r="F25">
-        <v>0.14880000054836273</v>
+        <v>0.18199999630451202</v>
       </c>
       <c r="G25">
-        <v>0.15449999272823334</v>
+        <v>0.19799999892711639</v>
       </c>
       <c r="H25">
-        <v>0.1550000011920929</v>
+        <v>0.16949999332427979</v>
       </c>
       <c r="I25">
-        <v>0.15530000627040863</v>
+        <v>0.16859999299049377</v>
       </c>
       <c r="J25">
-        <v>0.15770000219345093</v>
+        <v>0.17069999873638153</v>
       </c>
       <c r="K25">
-        <v>0.15590000152587891</v>
+        <v>0.24279999732971191</v>
       </c>
       <c r="L25">
-        <v>0.15150000154972076</v>
+        <v>0.24160000681877136</v>
       </c>
       <c r="M25">
-        <v>0.14939999580383301</v>
+        <v>0.22470000386238098</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
@@ -1052,40 +1049,40 @@
         <v>32</v>
       </c>
       <c r="B26">
-        <v>0.14419999718666077</v>
+        <v>0.1265999972820282</v>
       </c>
       <c r="C26">
-        <v>0.15590000152587891</v>
+        <v>0.12189999967813492</v>
       </c>
       <c r="D26">
-        <v>0.14699999988079071</v>
+        <v>0.1281999945640564</v>
       </c>
       <c r="E26">
-        <v>0.14890000224113464</v>
+        <v>0.13289999961853027</v>
       </c>
       <c r="F26">
-        <v>0.13699999451637268</v>
+        <v>0.12759999930858612</v>
       </c>
       <c r="G26">
-        <v>0.14679999649524689</v>
+        <v>0.13210000097751617</v>
       </c>
       <c r="H26">
-        <v>0.15659999847412109</v>
+        <v>0.16179999709129333</v>
       </c>
       <c r="I26">
-        <v>0.15659999847412109</v>
+        <v>0.16200000047683716</v>
       </c>
       <c r="J26">
-        <v>0.15109999477863312</v>
+        <v>0.16369999945163727</v>
       </c>
       <c r="K26">
-        <v>0.15440000593662262</v>
+        <v>0.25420001149177551</v>
       </c>
       <c r="L26">
-        <v>0.1632000058889389</v>
+        <v>0.23960000276565552</v>
       </c>
       <c r="M26">
-        <v>0.14710000157356262</v>
+        <v>0.22740000486373901</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
@@ -1093,40 +1090,40 @@
         <v>33</v>
       </c>
       <c r="B27">
-        <v>0.13339999318122864</v>
+        <v>0.11810000240802765</v>
       </c>
       <c r="C27">
-        <v>0.13459999859333038</v>
+        <v>0.12389999628067017</v>
       </c>
       <c r="D27">
-        <v>0.13689999282360077</v>
+        <v>0.12169999629259109</v>
       </c>
       <c r="E27">
-        <v>0.13699999451637268</v>
+        <v>0.12549999356269836</v>
       </c>
       <c r="F27">
-        <v>0.13750000298023224</v>
+        <v>0.1257999986410141</v>
       </c>
       <c r="G27">
-        <v>0.14339999854564667</v>
+        <v>0.12839999794960022</v>
       </c>
       <c r="H27">
-        <v>0.15049999952316284</v>
+        <v>0.16380000114440918</v>
       </c>
       <c r="I27">
-        <v>0.15919999778270721</v>
+        <v>0.16619999706745148</v>
       </c>
       <c r="J27">
-        <v>0.15620000660419464</v>
+        <v>0.17159999907016754</v>
       </c>
       <c r="K27">
-        <v>0.1598999947309494</v>
+        <v>0.2492000013589859</v>
       </c>
       <c r="L27">
-        <v>0.15569999814033508</v>
+        <v>0.24490000307559967</v>
       </c>
       <c r="M27">
-        <v>0.15629999339580536</v>
+        <v>0.24889999628067017</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
@@ -1134,40 +1131,40 @@
         <v>34</v>
       </c>
       <c r="B28">
-        <v>0.14429999887943268</v>
+        <v>0.14920000731945038</v>
       </c>
       <c r="C28">
-        <v>0.1542000025510788</v>
+        <v>0.13989999890327454</v>
       </c>
       <c r="D28">
-        <v>0.14910000562667847</v>
+        <v>0.14820000529289246</v>
       </c>
       <c r="E28">
-        <v>0.16509999334812164</v>
+        <v>0.15369999408721924</v>
       </c>
       <c r="F28">
-        <v>0.16709999740123749</v>
+        <v>0.15520000457763672</v>
       </c>
       <c r="G28">
-        <v>0.16529999673366547</v>
+        <v>0.15629999339580536</v>
       </c>
       <c r="H28">
-        <v>0.15899999439716339</v>
+        <v>0.19879999756813049</v>
       </c>
       <c r="I28">
-        <v>0.15610000491142273</v>
+        <v>0.1582999974489212</v>
       </c>
       <c r="J28">
-        <v>0.15670000016689301</v>
+        <v>0.17180000245571136</v>
       </c>
       <c r="K28">
-        <v>0.16730000078678131</v>
+        <v>0.23659999668598175</v>
       </c>
       <c r="L28">
-        <v>0.16760000586509705</v>
+        <v>0.24050000309944153</v>
       </c>
       <c r="M28">
-        <v>0.16470000147819519</v>
+        <v>0.23989999294281006</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
@@ -1175,40 +1172,40 @@
         <v>35</v>
       </c>
       <c r="B29">
-        <v>0.14980000257492065</v>
+        <v>0.17299999296665192</v>
       </c>
       <c r="C29">
-        <v>0.15209999680519104</v>
+        <v>0.18700000643730164</v>
       </c>
       <c r="D29">
-        <v>0.15299999713897705</v>
+        <v>0.20520000159740448</v>
       </c>
       <c r="E29">
-        <v>0.16099999845027924</v>
+        <v>0.20280000567436218</v>
       </c>
       <c r="F29">
-        <v>0.16699999570846558</v>
+        <v>0.19720000028610229</v>
       </c>
       <c r="G29">
-        <v>0.17299999296665192</v>
+        <v>0.20769999921321869</v>
       </c>
       <c r="H29">
-        <v>0.16339999437332153</v>
+        <v>0.21340000629425049</v>
       </c>
       <c r="I29">
-        <v>0.17209999263286591</v>
+        <v>0.21369999647140503</v>
       </c>
       <c r="J29">
-        <v>0.15629999339580536</v>
+        <v>0.17489999532699585</v>
       </c>
       <c r="K29">
-        <v>0.17110000550746918</v>
+        <v>0.24729999899864197</v>
       </c>
       <c r="L29">
-        <v>0.17329999804496765</v>
+        <v>0.24240000545978546</v>
       </c>
       <c r="M29">
-        <v>0.16449999809265137</v>
+        <v>0.23790000379085541</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
@@ -1216,40 +1213,40 @@
         <v>36</v>
       </c>
       <c r="B30">
-        <v>0.15279999375343323</v>
+        <v>0.17880000174045563</v>
       </c>
       <c r="C30">
-        <v>0.15770000219345093</v>
+        <v>0.20139999687671661</v>
       </c>
       <c r="D30">
-        <v>0.15999999642372131</v>
+        <v>0.20999999344348907</v>
       </c>
       <c r="E30">
-        <v>0.16120000183582306</v>
+        <v>0.22300000488758087</v>
       </c>
       <c r="F30">
-        <v>0.1648000031709671</v>
+        <v>0.22709999978542328</v>
       </c>
       <c r="G30">
-        <v>0.16699999570846558</v>
+        <v>0.21840000152587891</v>
       </c>
       <c r="H30">
-        <v>0.16599999368190765</v>
+        <v>0.22450000047683716</v>
       </c>
       <c r="I30">
-        <v>0.1695999950170517</v>
+        <v>0.22869999706745148</v>
       </c>
       <c r="J30">
-        <v>0.16150000691413879</v>
+        <v>0.18760000169277191</v>
       </c>
       <c r="K30">
-        <v>0.16699999570846558</v>
+        <v>0.23890000581741333</v>
       </c>
       <c r="L30">
-        <v>0.1590999960899353</v>
+        <v>0.24400000274181366</v>
       </c>
       <c r="M30">
-        <v>0.16699999570846558</v>
+        <v>0.22910000383853912</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
@@ -1257,40 +1254,40 @@
         <v>37</v>
       </c>
       <c r="B31">
-        <v>0.15119999647140503</v>
+        <v>0.18160000443458557</v>
       </c>
       <c r="C31">
-        <v>0.15119999647140503</v>
+        <v>0.19410000741481781</v>
       </c>
       <c r="D31">
-        <v>0.15109999477863312</v>
+        <v>0.21930000185966492</v>
       </c>
       <c r="E31">
-        <v>0.16140000522136688</v>
+        <v>0.23370000720024109</v>
       </c>
       <c r="F31">
-        <v>0.15870000422000885</v>
+        <v>0.23639999330043793</v>
       </c>
       <c r="G31">
-        <v>0.16660000383853912</v>
+        <v>0.23569999635219574</v>
       </c>
       <c r="H31">
-        <v>0.16750000417232513</v>
+        <v>0.22429999709129333</v>
       </c>
       <c r="I31">
-        <v>0.16349999606609344</v>
+        <v>0.21359999477863312</v>
       </c>
       <c r="J31">
-        <v>0.15690000355243683</v>
+        <v>0.18129999935626984</v>
       </c>
       <c r="K31">
-        <v>0.16820000112056732</v>
+        <v>0.24629999697208405</v>
       </c>
       <c r="L31">
-        <v>0.15549999475479126</v>
+        <v>0.24060000479221344</v>
       </c>
       <c r="M31">
-        <v>0.16259999573230743</v>
+        <v>0.24250000715255737</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
@@ -1298,40 +1295,40 @@
         <v>38</v>
       </c>
       <c r="B32">
-        <v>0.15999999642372131</v>
+        <v>0.16410000622272491</v>
       </c>
       <c r="C32">
-        <v>0.15449999272823334</v>
+        <v>0.18559999763965607</v>
       </c>
       <c r="D32">
-        <v>0.15610000491142273</v>
+        <v>0.19460000097751617</v>
       </c>
       <c r="E32">
-        <v>0.16099999845027924</v>
+        <v>0.23139999806880951</v>
       </c>
       <c r="F32">
-        <v>0.16110000014305115</v>
+        <v>0.23680000007152557</v>
       </c>
       <c r="G32">
-        <v>0.1664000004529953</v>
+        <v>0.24220000207424164</v>
       </c>
       <c r="H32">
-        <v>0.15770000219345093</v>
+        <v>0.20810000598430634</v>
       </c>
       <c r="I32">
-        <v>0.16050000488758087</v>
+        <v>0.18999999761581421</v>
       </c>
       <c r="J32">
-        <v>0.15800000727176666</v>
+        <v>0.17779999971389771</v>
       </c>
       <c r="K32">
-        <v>0.16349999606609344</v>
+        <v>0.23999999463558197</v>
       </c>
       <c r="L32">
-        <v>0.1664000004529953</v>
+        <v>0.2328999936580658</v>
       </c>
       <c r="M32">
-        <v>0.16869999468326569</v>
+        <v>0.2312999963760376</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1510,40 +1507,40 @@
         <v>31</v>
       </c>
       <c r="B57">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="C57">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="D57">
-        <v>132</v>
+        <v>204</v>
       </c>
       <c r="E57">
-        <v>65</v>
+        <v>167</v>
       </c>
       <c r="F57">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="G57">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="H57">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="I57">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="J57">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="K57">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="L57">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="M57">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
@@ -1551,40 +1548,40 @@
         <v>32</v>
       </c>
       <c r="B58">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="C58">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="D58">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="E58">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="F58">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="G58">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="H58">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="I58">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="J58">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="K58">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="L58">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="M58">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
@@ -1592,40 +1589,40 @@
         <v>33</v>
       </c>
       <c r="B59">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C59">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="D59">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="E59">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="F59">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="G59">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="H59">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="I59">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="J59">
+        <v>94</v>
+      </c>
+      <c r="K59">
+        <v>100</v>
+      </c>
+      <c r="L59">
+        <v>99</v>
+      </c>
+      <c r="M59">
         <v>101</v>
-      </c>
-      <c r="K59">
-        <v>86</v>
-      </c>
-      <c r="L59">
-        <v>78</v>
-      </c>
-      <c r="M59">
-        <v>79</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
@@ -1633,40 +1630,40 @@
         <v>34</v>
       </c>
       <c r="B60">
-        <v>131</v>
+        <v>268</v>
       </c>
       <c r="C60">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="D60">
-        <v>168</v>
+        <v>268</v>
       </c>
       <c r="E60">
-        <v>158</v>
+        <v>249</v>
       </c>
       <c r="F60">
-        <v>162</v>
+        <v>246</v>
       </c>
       <c r="G60">
-        <v>174</v>
+        <v>263</v>
       </c>
       <c r="H60">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="I60">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J60">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="K60">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="L60">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="M60">
-        <v>81</v>
+        <v>97</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
@@ -1674,40 +1671,40 @@
         <v>35</v>
       </c>
       <c r="B61">
-        <v>155</v>
+        <v>548</v>
       </c>
       <c r="C61">
-        <v>176</v>
+        <v>586</v>
       </c>
       <c r="D61">
-        <v>164</v>
+        <v>686</v>
       </c>
       <c r="E61">
-        <v>216</v>
+        <v>505</v>
       </c>
       <c r="F61">
-        <v>224</v>
+        <v>464</v>
       </c>
       <c r="G61">
-        <v>219</v>
+        <v>535</v>
       </c>
       <c r="H61">
-        <v>192</v>
+        <v>739</v>
       </c>
       <c r="I61">
-        <v>99</v>
+        <v>145</v>
       </c>
       <c r="J61">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K61">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="L61">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="M61">
-        <v>80</v>
+        <v>102</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
@@ -1715,40 +1712,40 @@
         <v>36</v>
       </c>
       <c r="B62">
-        <v>154</v>
+        <v>660</v>
       </c>
       <c r="C62">
-        <v>186</v>
+        <v>768</v>
       </c>
       <c r="D62">
-        <v>180</v>
+        <v>817</v>
       </c>
       <c r="E62">
-        <v>208</v>
+        <v>687</v>
       </c>
       <c r="F62">
-        <v>233</v>
+        <v>711</v>
       </c>
       <c r="G62">
-        <v>237</v>
+        <v>668</v>
       </c>
       <c r="H62">
-        <v>199</v>
+        <v>913</v>
       </c>
       <c r="I62">
-        <v>122</v>
+        <v>450</v>
       </c>
       <c r="J62">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="K62">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L62">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="M62">
-        <v>179</v>
+        <v>102</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
@@ -1756,40 +1753,40 @@
         <v>37</v>
       </c>
       <c r="B63">
-        <v>159</v>
+        <v>665</v>
       </c>
       <c r="C63">
-        <v>184</v>
+        <v>805</v>
       </c>
       <c r="D63">
-        <v>172</v>
+        <v>1116</v>
       </c>
       <c r="E63">
-        <v>209</v>
+        <v>978</v>
       </c>
       <c r="F63">
-        <v>219</v>
+        <v>1041</v>
       </c>
       <c r="G63">
-        <v>228</v>
+        <v>966</v>
       </c>
       <c r="H63">
-        <v>190</v>
+        <v>783</v>
       </c>
       <c r="I63">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="J63">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="K63">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="L63">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="M63">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
@@ -1797,40 +1794,40 @@
         <v>38</v>
       </c>
       <c r="B64">
-        <v>143</v>
+        <v>425</v>
       </c>
       <c r="C64">
-        <v>172</v>
+        <v>532</v>
       </c>
       <c r="D64">
-        <v>159</v>
+        <v>593</v>
       </c>
       <c r="E64">
-        <v>193</v>
+        <v>790</v>
       </c>
       <c r="F64">
-        <v>199</v>
+        <v>802</v>
       </c>
       <c r="G64">
-        <v>214</v>
+        <v>854</v>
       </c>
       <c r="H64">
-        <v>164</v>
+        <v>437</v>
       </c>
       <c r="I64">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="J64">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="K64">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="L64">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="M64">
-        <v>80</v>
+        <v>110</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -1960,7 +1957,7 @@
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
@@ -2009,40 +2006,40 @@
         <v>31</v>
       </c>
       <c r="B89">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="C89">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D89">
-        <v>97</v>
+        <v>173</v>
       </c>
       <c r="E89">
-        <v>32</v>
+        <v>140</v>
       </c>
       <c r="F89">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="G89">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="H89">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="I89">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="J89">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="K89">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="L89">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="M89">
-        <v>26</v>
+        <v>51</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
@@ -2050,40 +2047,40 @@
         <v>32</v>
       </c>
       <c r="B90">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C90">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="D90">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="E90">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="F90">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="G90">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="H90">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I90">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J90">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K90">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="L90">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="M90">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
@@ -2091,40 +2088,40 @@
         <v>33</v>
       </c>
       <c r="B91">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C91">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D91">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E91">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F91">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="G91">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H91">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I91">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J91">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K91">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="L91">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="M91">
-        <v>24</v>
+        <v>45</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
@@ -2132,40 +2129,40 @@
         <v>34</v>
       </c>
       <c r="B92">
-        <v>89</v>
+        <v>244</v>
       </c>
       <c r="C92">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="D92">
-        <v>105</v>
+        <v>258</v>
       </c>
       <c r="E92">
-        <v>113</v>
+        <v>235</v>
       </c>
       <c r="F92">
-        <v>124</v>
+        <v>225</v>
       </c>
       <c r="G92">
-        <v>137</v>
+        <v>253</v>
       </c>
       <c r="H92">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I92">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J92">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K92">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="L92">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="M92">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
@@ -2173,40 +2170,40 @@
         <v>35</v>
       </c>
       <c r="B93">
-        <v>107</v>
+        <v>554</v>
       </c>
       <c r="C93">
-        <v>131</v>
+        <v>605</v>
       </c>
       <c r="D93">
-        <v>130</v>
+        <v>713</v>
       </c>
       <c r="E93">
-        <v>173</v>
+        <v>518</v>
       </c>
       <c r="F93">
-        <v>190</v>
+        <v>482</v>
       </c>
       <c r="G93">
-        <v>183</v>
+        <v>560</v>
       </c>
       <c r="H93">
-        <v>159</v>
+        <v>772</v>
       </c>
       <c r="I93">
-        <v>45</v>
+        <v>101</v>
       </c>
       <c r="J93">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="K93">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="L93">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="M93">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
@@ -2214,40 +2211,40 @@
         <v>36</v>
       </c>
       <c r="B94">
-        <v>109</v>
+        <v>698</v>
       </c>
       <c r="C94">
-        <v>141</v>
+        <v>820</v>
       </c>
       <c r="D94">
-        <v>137</v>
+        <v>852</v>
       </c>
       <c r="E94">
-        <v>171</v>
+        <v>728</v>
       </c>
       <c r="F94">
-        <v>199</v>
+        <v>749</v>
       </c>
       <c r="G94">
-        <v>201</v>
+        <v>704</v>
       </c>
       <c r="H94">
-        <v>157</v>
+        <v>973</v>
       </c>
       <c r="I94">
-        <v>76</v>
+        <v>243</v>
       </c>
       <c r="J94">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="K94">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="L94">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="M94">
-        <v>27</v>
+        <v>45</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
@@ -2255,40 +2252,40 @@
         <v>37</v>
       </c>
       <c r="B95">
-        <v>110</v>
+        <v>690</v>
       </c>
       <c r="C95">
-        <v>140</v>
+        <v>849</v>
       </c>
       <c r="D95">
-        <v>128</v>
+        <v>1213</v>
       </c>
       <c r="E95">
-        <v>168</v>
+        <v>1036</v>
       </c>
       <c r="F95">
-        <v>190</v>
+        <v>1130</v>
       </c>
       <c r="G95">
-        <v>196</v>
+        <v>1043</v>
       </c>
       <c r="H95">
-        <v>153</v>
+        <v>847</v>
       </c>
       <c r="I95">
-        <v>50</v>
+        <v>126</v>
       </c>
       <c r="J95">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="K95">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="L95">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="M95">
-        <v>30</v>
+        <v>49</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
@@ -2296,40 +2293,40 @@
         <v>38</v>
       </c>
       <c r="B96">
-        <v>97</v>
+        <v>412</v>
       </c>
       <c r="C96">
-        <v>127</v>
+        <v>543</v>
       </c>
       <c r="D96">
-        <v>117</v>
+        <v>610</v>
       </c>
       <c r="E96">
-        <v>150</v>
+        <v>819</v>
       </c>
       <c r="F96">
-        <v>158</v>
+        <v>843</v>
       </c>
       <c r="G96">
-        <v>178</v>
+        <v>889</v>
       </c>
       <c r="H96">
-        <v>121</v>
+        <v>437</v>
       </c>
       <c r="I96">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="J96">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="K96">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="L96">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="M96">
-        <v>29</v>
+        <v>49</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -2337,7 +2334,7 @@
         <v>39</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -2347,7 +2344,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FC7F55B-537E-4A25-B78C-4B6DADB99477}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F132AB5-7C5F-4AF8-9B00-7C783989336B}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
